--- a/deliverables/CNF_API_Classification.xlsx
+++ b/deliverables/CNF_API_Classification.xlsx
@@ -428,17 +428,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wrap existing custom object</t>
+          <t xml:space="preserve">Wrap existing CDS view</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZLE526 already returns the pending DI/MRN list</t>
+          <t xml:space="preserve">CDS zsd_mrn_pending_cds_opt already returns the pending-MRN set</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under Option C the portal reads Pending MRN from DSP-to-T2; SAP surface may reduce to little or nothing</t>
+          <t xml:space="preserve">Expose the CDS; honour TVARVC exclusion (Q-047). Pending = dispatched minus received, per delivery</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DigiGST cockpit /DIGIGST/INVP - NOT SAP Document and Reporting Compliance</t>
+          <t xml:space="preserve">DigiGST /DIGIGST/INVP; E-Way number in /DIGIGST/OWARD_H-EWBNUMBER. SAP eDocument framework ALSO present (EDOC_COCKPIT)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration surface unknown; window evaluation; E-Way linkage guard</t>
+          <t xml:space="preserve">Window evaluation; branch to credit note; E-Way linkage guard</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -829,136 +829,148 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPTION C IMPACT</t>
+          <t xml:space="preserve">S/4HANA 2022 CONFIRMED</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Architecture Option C (D-014) serves Orders, Deliveries and Invoices live from Hybris T1, and Pending MRN / STO / Stock Ageing from Datasphere to T2. Most read APIs therefore leave SAP scope. What remains on the SAP side is the write commands plus two real-time reads (Stock Availability, Shipment Cost estimate) - neither of which appears on the Option C diagram. See Q-037, Q-038.</t>
+          <t xml:space="preserve">Backend verified as S/4HANA 2022 on-premise, ABAP Platform 2022, three-system landscape DS4/QS4/PS4 (D-018). Released APIs and CDS exist and RAP is available - but only 7 A2X services are registered on this Gateway and none of the delivery/billing/material ones. See Q-045 (activation) and Q-046 (SEGW vs RAP).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NEW - UNOWNED</t>
+          <t xml:space="preserve">OPTION C IMPACT</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">S/4 to T1 outbound push for Deliveries and Invoices. Option C reads them live from T1, but they are created in S/4. No trigger, latency, owner or mechanism specified, and it is in no API inventory. See Q-037.</t>
+          <t xml:space="preserve">Architecture Option C (D-014) serves Orders, Deliveries and Invoices live from Hybris T1, and Pending MRN / STO / Stock Ageing from Datasphere to T2. Most read APIs therefore leave SAP scope. What remains on the SAP side is the write commands plus two real-time reads (Stock Availability, Shipment Cost estimate) - neither of which appears on the Option C diagram. See Q-037, Q-038.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SCOPE NOTE</t>
+          <t xml:space="preserve">NEW - UNOWNED</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">API-01 to API-09 correspond one-to-one with the client process register. API-10 Modify DI is a proposed addition: Create DI has no amend path without it, and a delivery must be correctable before goods issue.</t>
+          <t xml:space="preserve">S/4 to T1 outbound push for Deliveries and Invoices. Option C reads them live from T1, but they are created in S/4. No trigger, latency, owner or mechanism specified, and it is in no API inventory. See Q-037.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">SCOPE NOTE</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-01 to API-09 correspond one-to-one with the client process register. API-10 Modify DI is a proposed addition: Create DI has no amend path without it, and a delivery must be correctable before goods issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">DISTRIBUTION</t>
         </is>
       </c>
-      <c r="B18" s="0" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">4 Standard (S)</t>
         </is>
       </c>
-      <c r="C18" s="0" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1 Custom over standard (C)</t>
         </is>
       </c>
-      <c r="D18" s="0" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2 New construction (X)</t>
         </is>
       </c>
-      <c r="E18" s="0" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1 Wrap existing (W), 1 Third-party (T), 1 scope-unconfirmed</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLASSIFICATION KEY</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">S - Standard</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A delivered SAP API, BAPI or released service performs the business operation. ABAP work is a thin service wrapper: protocol mapping, authorization, idempotency, error shaping. No business logic.</t>
+          <t xml:space="preserve">CLASSIFICATION KEY</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">C - Custom over standard</t>
+          <t xml:space="preserve">S - Standard</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No single standard API returns the required shape, but every underlying source is standard. Composite CDS view or application class over standard reads.</t>
+          <t xml:space="preserve">A delivered SAP API, BAPI or released service performs the business operation. ABAP work is a thin service wrapper: protocol mapping, authorization, idempotency, error shaping. No business logic.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">X - New construction</t>
+          <t xml:space="preserve">C - Custom over standard</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The required behaviour has no standard equivalent. Must be designed and built: orchestration, state management, pre-document simulation, external coordination.</t>
+          <t xml:space="preserve">No single standard API returns the required shape, but every underlying source is standard. Composite CDS view or application class over standard reads.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">W - Wrap existing custom object</t>
+          <t xml:space="preserve">X - New construction</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The client already has a custom report or object implementing the logic (ZLE526, ZSDR512N, ZLE520, ZSDR513, ZMM5013). Expose or reuse rather than rebuild. Effort depends on whether it is RFC-capable - see Q-043.</t>
+          <t xml:space="preserve">The required behaviour has no standard equivalent. Must be designed and built: orchestration, state management, pre-document simulation, external coordination.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">W - Wrap existing custom object</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The client already implements the logic. VERIFIED 2026-08-04: the T-codes are report programs, but underneath them sit consumable artifacts - CDS view zsd_mrn_pending_cds_opt for pending MRN, and RFC-enabled FM ZSD_PENDING_ORDER_FM for pending orders. Expose those rather than rebuild.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">T - Third-party add-on</t>
         </is>
       </c>
-      <c r="B25" s="0" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Behaviour is delivered by a non-SAP add-on (DigiGST). Neither SAP standard nor greenfield custom - integration against a vendor product with its own tables and support model.</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27"/>
+    <row r="28"/>
   </sheetData>
   <autoFilter ref="A3:H13"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
@@ -1036,27 +1048,27 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">W</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">All underlying document reads are standard</t>
+          <t xml:space="preserve">An existing CDS view (zsd_mrn_pending_cds_opt) already returns the pending-MRN set with all filters</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cross-document composite, tri-state receipt status, pending-quantity derivation</t>
+          <t xml:space="preserve">Expose the CDS as a service; honour the TVARVC exclusion list; decide on the residual matdoc reconciliation loop</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Build the composite over released views, not direct table SELECTs, where the release allows</t>
+          <t xml:space="preserve">UPGRADED 2026-08-04 - far cheaper than the composite build originally estimated. Verified from ZLE_MRN_PENDING_REPORT source</t>
         </is>
       </c>
     </row>
